--- a/PUEYRREDON 1494/Agosto/PUEYRREDON Agosto.xlsx
+++ b/PUEYRREDON 1494/Agosto/PUEYRREDON Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526A91AB-E863-4823-9701-8AC5CB318D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F30F9A-99C5-4635-B878-3A53717CD1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$116</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$115</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="171">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -471,30 +471,9 @@
     <t>Transf 17/07</t>
   </si>
   <si>
-    <t>VTO 14/08</t>
-  </si>
-  <si>
-    <t>PERÍODO: JULIO</t>
-  </si>
-  <si>
-    <t>Mes de JULIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JULIO</t>
-  </si>
-  <si>
-    <t>Mantenimiento Ascensores - Mes de JULIO</t>
-  </si>
-  <si>
-    <t>Efect 14/07</t>
-  </si>
-  <si>
     <t>Debito 14/07</t>
   </si>
   <si>
-    <t>Mantenimiento Ascensores - Mes de JUNIO</t>
-  </si>
-  <si>
     <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas - Se deben $500.000</t>
   </si>
   <si>
@@ -504,12 +483,6 @@
     <t>PMC 28/07</t>
   </si>
   <si>
-    <t>PMC 12/07</t>
-  </si>
-  <si>
-    <t>Transf 28/07</t>
-  </si>
-  <si>
     <t>Debito 30/07</t>
   </si>
   <si>
@@ -538,6 +511,33 @@
   </si>
   <si>
     <t>EL PAGO NO IDENTIFICADO DEL MES PASADO ES DE ELLA - RATON MARIELA</t>
+  </si>
+  <si>
+    <t>VTO 15/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>Mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Mantenimiento Ascensores - Mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Transf 19/08</t>
+  </si>
+  <si>
+    <t>Transf 01/08</t>
+  </si>
+  <si>
+    <t>Efect 02/08</t>
+  </si>
+  <si>
+    <t>PMC 12/08</t>
   </si>
 </sst>
 </file>
@@ -545,14 +545,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="&quot;Bs&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;Bs&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1222,11 +1222,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1234,7 +1234,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1242,16 +1242,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1262,8 +1262,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1273,25 +1273,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1299,11 +1299,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,96 +1317,96 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1431,25 +1431,42 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1457,42 +1474,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1502,21 +1507,18 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1872,28 +1874,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M119"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="141"/>
       <c r="B1" s="142"/>
       <c r="C1" s="143"/>
       <c r="D1" s="143"/>
       <c r="E1" s="144"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="145"/>
       <c r="B2" s="137" t="s">
         <v>0</v>
@@ -1902,7 +1904,7 @@
       <c r="D2" s="137"/>
       <c r="E2" s="146"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="145"/>
       <c r="B3" s="137" t="s">
         <v>1</v>
@@ -1911,7 +1913,7 @@
       <c r="D3" s="137"/>
       <c r="E3" s="146"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="145"/>
       <c r="B4" s="138" t="s">
         <v>2</v>
@@ -1922,7 +1924,7 @@
       </c>
       <c r="E4" s="146"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="145" t="s">
         <v>4</v>
       </c>
@@ -1933,12 +1935,12 @@
       <c r="D5" s="136"/>
       <c r="E5" s="147"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="145" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="136" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C6" s="136"/>
       <c r="D6" s="137" t="s">
@@ -1946,7 +1948,7 @@
       </c>
       <c r="E6" s="147"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="148" t="s">
         <v>8</v>
       </c>
@@ -1955,60 +1957,60 @@
       <c r="D7" s="149"/>
       <c r="E7" s="150"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="166" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="154"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="154"/>
-      <c r="C10" s="154"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="154"/>
-      <c r="C11" s="154"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="155" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="156"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="133"/>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167" t="s">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="159" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="156"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="156"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="156"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -2017,7 +2019,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
         <v>11</v>
       </c>
@@ -2026,7 +2028,7 @@
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
@@ -2037,7 +2039,7 @@
       </c>
       <c r="E23" s="80"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
@@ -2048,7 +2050,7 @@
       </c>
       <c r="E24" s="80"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
@@ -2060,7 +2062,7 @@
       <c r="E25" s="80"/>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2068,7 +2070,7 @@
       <c r="E26" s="80"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
         <v>15</v>
       </c>
@@ -2081,7 +2083,7 @@
       <c r="E27" s="81"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2089,7 +2091,7 @@
       <c r="E28" s="80"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2097,7 +2099,7 @@
       <c r="E29" s="80"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="57" t="s">
         <v>15</v>
       </c>
@@ -2109,7 +2111,7 @@
       </c>
       <c r="E30" s="81"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="23" t="s">
         <v>16</v>
       </c>
@@ -2122,7 +2124,7 @@
       </c>
       <c r="F31" s="15"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="32" t="s">
         <v>17</v>
       </c>
@@ -2131,7 +2133,7 @@
       <c r="D32" s="123"/>
       <c r="E32" s="83"/>
     </row>
-    <row r="33" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="64" t="s">
         <v>18</v>
       </c>
@@ -2139,17 +2141,17 @@
         <v>20</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="120">
+      <c r="D33" s="191">
         <v>35000</v>
       </c>
       <c r="E33" s="84"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="120">
@@ -2157,10 +2159,10 @@
       </c>
       <c r="E34" s="84"/>
       <c r="H34" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="23" t="s">
         <v>21</v>
       </c>
@@ -2172,7 +2174,7 @@
         <v>170100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="30" t="s">
         <v>22</v>
       </c>
@@ -2181,29 +2183,29 @@
       <c r="D36" s="125"/>
       <c r="E36" s="66"/>
     </row>
-    <row r="37" spans="1:8" s="36" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="168" t="s">
+    <row r="37" spans="1:8" s="36" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="157"/>
+      <c r="B37" s="158"/>
       <c r="C37" s="55"/>
       <c r="D37" s="126">
         <v>87562.7</v>
       </c>
       <c r="E37" s="106"/>
     </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="168" t="s">
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="160" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="157"/>
+      <c r="B38" s="158"/>
       <c r="C38" s="55"/>
       <c r="D38" s="127">
         <v>6646.91</v>
       </c>
       <c r="E38" s="106"/>
     </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23" t="s">
         <v>25</v>
       </c>
@@ -2215,7 +2217,7 @@
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
         <v>26</v>
       </c>
@@ -2224,70 +2226,70 @@
       <c r="D40" s="128"/>
       <c r="E40" s="87"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="53"/>
-      <c r="D41" s="127">
-        <v>620508.89</v>
+      <c r="D41" s="188">
+        <v>380468.13</v>
       </c>
       <c r="E41" s="107" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G41" s="104"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="127">
-        <v>32378.28</v>
+      <c r="D42" s="188">
+        <v>19706.62</v>
       </c>
       <c r="E42" s="108" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="str">
         <f>A42</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="127">
-        <v>102414.9</v>
+      <c r="D43" s="188">
+        <v>63551.19</v>
       </c>
       <c r="E43" s="108" t="str">
         <f>E42</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de JULIO</v>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="127">
-        <v>6475.66</v>
+      <c r="D44" s="188">
+        <v>3941.32</v>
       </c>
       <c r="E44" s="109" t="str">
         <f>E43</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="23" t="s">
         <v>31</v>
       </c>
@@ -2296,10 +2298,10 @@
       <c r="D45" s="129"/>
       <c r="E45" s="86">
         <f>SUM(D41:D44)</f>
-        <v>761777.7300000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>467667.26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
         <v>32</v>
       </c>
@@ -2308,633 +2310,619 @@
       <c r="D46" s="128"/>
       <c r="E46" s="87"/>
     </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="127">
-        <v>36700</v>
+      <c r="D47" s="188">
+        <v>44625</v>
       </c>
       <c r="E47" s="90" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G47" s="112"/>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
-        <v>152</v>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="127">
-        <v>42500</v>
+        <v>86610.08</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>160</v>
-      </c>
-      <c r="G48" s="112"/>
-    </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="127">
-        <v>86610.08</v>
+        <v>25000</v>
       </c>
       <c r="E49" s="90" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" s="5"/>
+        <v>151</v>
+      </c>
+      <c r="G49" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="189" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="190"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="127">
-        <v>25000</v>
+      <c r="D50" s="188">
+        <v>135000</v>
       </c>
       <c r="E50" s="90" t="s">
-        <v>158</v>
-      </c>
-      <c r="G50" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="171" t="s">
-        <v>162</v>
-      </c>
-      <c r="B51" s="172"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="127">
-        <v>135000</v>
+        <v>119000</v>
       </c>
       <c r="E51" s="90" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="127">
-        <v>119000</v>
+        <v>35626.879999999997</v>
       </c>
       <c r="E52" s="90" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="127">
-        <v>35626.879999999997</v>
+      <c r="D53" s="188">
+        <v>30000</v>
       </c>
       <c r="E53" s="90" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B54" s="5"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="161" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="162"/>
       <c r="C54" s="5"/>
       <c r="D54" s="127">
-        <v>30000</v>
-      </c>
-      <c r="E54" s="90" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="169" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55" s="170"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="127">
         <v>500000</v>
       </c>
-      <c r="E55" s="90"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="156" t="s">
+      <c r="E54" s="90"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="157" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="157"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="152">
+      <c r="B55" s="158"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="152">
         <v>67030</v>
       </c>
-      <c r="E56" s="108" t="s">
+      <c r="E55" s="108" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="23" t="s">
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="23" t="s">
         <v>35</v>
+      </c>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="124"/>
+      <c r="E56" s="86">
+        <f>SUM(D47:D55)</f>
+        <v>1042891.96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="32" t="s">
+        <v>36</v>
       </c>
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="124"/>
-      <c r="E57" s="86">
-        <f>SUM(D47:D56)</f>
-        <v>1077466.96</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="124"/>
-      <c r="E58" s="89"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="53"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="88"/>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="23" t="s">
+      <c r="E57" s="89"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="53"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="88"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="92">
-        <f>SUM(D59:D59)</f>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="92">
+        <f>SUM(D58:D58)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="32" t="s">
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="122"/>
-      <c r="E61" s="89"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="65"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="122"/>
+      <c r="E60" s="89"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="127">
+        <v>48482.26</v>
+      </c>
+      <c r="E61" s="93"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="127">
-        <v>48482.26</v>
-      </c>
-      <c r="E62" s="93"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="127">
         <v>49082</v>
       </c>
-      <c r="E63" s="91"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="52" t="s">
+      <c r="E62" s="91"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="52"/>
-      <c r="C64" s="52"/>
-      <c r="D64" s="94"/>
-      <c r="E64" s="86">
-        <f>SUM(D62:D63)</f>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="94"/>
+      <c r="E63" s="86">
+        <f>SUM(D61:D62)</f>
         <v>97564.260000000009</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="80"/>
-      <c r="E65" s="95"/>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="25" t="s">
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="95"/>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="96"/>
-      <c r="E66" s="97">
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="96"/>
+      <c r="E65" s="97">
         <v>529019.43999999994</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-      <c r="D67" s="98"/>
-      <c r="E67" s="99"/>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="D66" s="98"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="43"/>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="100"/>
+      <c r="E67" s="101">
+        <f>(SUM(E31:E65))</f>
+        <v>2871314.53</v>
+      </c>
       <c r="F67" s="43"/>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="10"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="100"/>
-      <c r="E68" s="101">
-        <f>(SUM(E31:E66))</f>
-        <v>3199999.9999999995</v>
-      </c>
-      <c r="F68" s="43"/>
+      <c r="G67" s="112"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D68" s="98"/>
+      <c r="E68" s="98"/>
       <c r="G68" s="112"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D69" s="98"/>
       <c r="E69" s="98"/>
-      <c r="G69" s="112"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="98"/>
-      <c r="E70" s="98"/>
-    </row>
-    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+    </row>
+    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B71" s="12"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="102"/>
-      <c r="E71" s="103"/>
-    </row>
-    <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="156" t="s">
-        <v>167</v>
-      </c>
-      <c r="B72" s="158"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="162">
+      <c r="B70" s="12"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="102"/>
+      <c r="E70" s="103"/>
+    </row>
+    <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="157" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="165"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="169">
         <v>181000</v>
       </c>
-      <c r="E72" s="164"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="159"/>
-      <c r="B73" s="160"/>
+      <c r="E71" s="171"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="166"/>
+      <c r="B72" s="167"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="170"/>
+      <c r="E72" s="172"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="157"/>
+      <c r="B73" s="158"/>
       <c r="C73" s="53"/>
-      <c r="D73" s="163"/>
-      <c r="E73" s="165"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="156"/>
-      <c r="B74" s="157"/>
-      <c r="C74" s="53"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="131"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="50"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58">
-        <f>SUM(D72:D74)</f>
+      <c r="D73" s="34"/>
+      <c r="E73" s="131"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="50"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="58">
+        <f>SUM(D71:D73)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="25" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="113"/>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="113"/>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B79" s="10"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="67">
-        <f>E75+E77</f>
+      <c r="B78" s="10"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="67">
+        <f>E74+E76</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="79">
+        <f>E67</f>
+        <v>2871314.53</v>
+      </c>
+      <c r="D80" s="43"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B81" s="79">
-        <f>E68</f>
-        <v>3199999.9999999995</v>
-      </c>
-      <c r="D81" s="43"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E67-E65</f>
+        <v>2342295.09</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="78" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B82" s="79">
-        <f>E68-E66</f>
-        <v>2670980.5599999996</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E78-E76</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="78" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B83" s="79">
-        <f>E79-E77</f>
+        <f>E78</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="78" t="s">
-        <v>48</v>
-      </c>
-      <c r="B84" s="79">
-        <f>E79</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="153"/>
-      <c r="B87" s="154"/>
-      <c r="C87" s="154"/>
-      <c r="D87" s="154"/>
-      <c r="E87" s="154"/>
-    </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="154"/>
-      <c r="B88" s="154"/>
-      <c r="C88" s="154"/>
-      <c r="D88" s="154"/>
-      <c r="E88" s="154"/>
-    </row>
-    <row r="89" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="154"/>
-      <c r="B89" s="154"/>
-      <c r="C89" s="154"/>
-      <c r="D89" s="154"/>
-      <c r="E89" s="154"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="163"/>
+      <c r="B86" s="156"/>
+      <c r="C86" s="156"/>
+      <c r="D86" s="156"/>
+      <c r="E86" s="156"/>
+    </row>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="156"/>
+      <c r="B87" s="156"/>
+      <c r="C87" s="156"/>
+      <c r="D87" s="156"/>
+      <c r="E87" s="156"/>
+    </row>
+    <row r="88" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="156"/>
+      <c r="B88" s="156"/>
+      <c r="C88" s="156"/>
+      <c r="D88" s="156"/>
+      <c r="E88" s="156"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B91" s="38"/>
-      <c r="C91" s="17"/>
-    </row>
-    <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="28" t="s">
+      <c r="B90" s="38"/>
+      <c r="C90" s="17"/>
+    </row>
+    <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B92" s="111">
+      <c r="B91" s="111">
         <v>-1000157.7574999998</v>
       </c>
-      <c r="C92" s="19"/>
-    </row>
-    <row r="93" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="18" t="s">
+      <c r="C91" s="19"/>
+    </row>
+    <row r="92" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B93" s="39">
+      <c r="B92" s="39">
         <f>PRORRATEO!H25</f>
         <v>2893536.18</v>
       </c>
+      <c r="C92" s="17"/>
+    </row>
+    <row r="93" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" s="47"/>
       <c r="C93" s="17"/>
     </row>
-    <row r="94" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B94" s="47"/>
+    <row r="94" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="151" t="s">
+        <v>157</v>
+      </c>
+      <c r="B94" s="47">
+        <v>-8829</v>
+      </c>
       <c r="C94" s="17"/>
     </row>
-    <row r="95" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="151" t="s">
-        <v>166</v>
-      </c>
-      <c r="B95" s="47">
-        <v>-8829</v>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B95" s="91">
+        <f>B114</f>
+        <v>262000</v>
       </c>
       <c r="C95" s="17"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B96" s="91">
-        <f>B115</f>
-        <v>262000</v>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" s="47">
+        <f>-B81</f>
+        <v>-2342295.09</v>
       </c>
       <c r="C96" s="17"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="37" t="s">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B97" s="47">
+        <f>-(B82)</f>
+        <v>-181000</v>
+      </c>
+      <c r="C97" s="17"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" s="110">
+        <f>SUM(B91:B97)</f>
+        <v>-376745.66749999952</v>
+      </c>
+      <c r="C98" s="20"/>
+    </row>
+    <row r="99" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="40"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="43"/>
+    </row>
+    <row r="100" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="41"/>
+      <c r="C100" s="20"/>
+    </row>
+    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="40"/>
+      <c r="C101" s="35"/>
+    </row>
+    <row r="102" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="33"/>
+      <c r="C102" s="35"/>
+      <c r="D102" s="46"/>
+    </row>
+    <row r="103" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B103" s="34">
+        <v>0</v>
+      </c>
+      <c r="C103" s="35"/>
+    </row>
+    <row r="104" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B104" s="33">
+        <v>0</v>
+      </c>
+      <c r="C104" s="20"/>
+      <c r="D104" s="43"/>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B97" s="47">
-        <f>-B82</f>
-        <v>-2670980.5599999996</v>
-      </c>
-      <c r="C97" s="17"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B98" s="47">
-        <f>-(B83)</f>
-        <v>-181000</v>
-      </c>
-      <c r="C98" s="17"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B99" s="110">
-        <f>SUM(B92:B98)</f>
-        <v>-705431.13749999925</v>
-      </c>
-      <c r="C99" s="20"/>
-    </row>
-    <row r="100" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="40"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="43"/>
-    </row>
-    <row r="101" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="41"/>
-      <c r="C101" s="20"/>
-    </row>
-    <row r="102" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="40"/>
-      <c r="C102" s="35"/>
-    </row>
-    <row r="103" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B103" s="33"/>
-      <c r="C103" s="35"/>
-      <c r="D103" s="46"/>
-    </row>
-    <row r="104" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B104" s="34">
-        <v>0</v>
-      </c>
-      <c r="C104" s="35"/>
-    </row>
-    <row r="105" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="B105" s="33">
         <v>0</v>
       </c>
       <c r="C105" s="20"/>
-      <c r="D105" s="43"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B106" s="33">
         <v>0</v>
       </c>
-      <c r="C106" s="20"/>
-    </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B107" s="33">
+      <c r="C106" s="22"/>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" s="48">
+        <f>SUM(B103:B106)</f>
         <v>0</v>
       </c>
-      <c r="C107" s="22"/>
-    </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B108" s="48">
-        <f>SUM(B104:B107)</f>
-        <v>0</v>
-      </c>
-      <c r="C108" s="17"/>
-    </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="155" t="s">
+      <c r="C107" s="17"/>
+    </row>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="164" t="s">
         <v>59</v>
       </c>
-      <c r="B111" s="154"/>
-      <c r="C111" s="154"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="154"/>
-      <c r="B112" s="154"/>
-      <c r="C112" s="154"/>
-    </row>
-    <row r="113" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="55" t="s">
-        <v>169</v>
-      </c>
-      <c r="B113" s="33">
+      <c r="B110" s="156"/>
+      <c r="C110" s="156"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="156"/>
+      <c r="B111" s="156"/>
+      <c r="C111" s="156"/>
+    </row>
+    <row r="112" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B112" s="33">
         <v>262000</v>
       </c>
-      <c r="C113" s="33">
+      <c r="C112" s="33">
         <v>40000</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="55"/>
-      <c r="B114" s="33"/>
-      <c r="C114" s="40"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="44" t="s">
+    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="55"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="40"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B115" s="105">
-        <f>SUM(B113:B114)</f>
+      <c r="B114" s="105">
+        <f>SUM(B112:B113)</f>
         <v>262000</v>
       </c>
-      <c r="C115" s="45"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M116" s="8"/>
-    </row>
-    <row r="117" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="161"/>
-      <c r="B117" s="154"/>
-      <c r="C117" s="154"/>
-      <c r="D117" s="154"/>
-      <c r="E117" s="154"/>
-    </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="154"/>
-      <c r="B118" s="154"/>
-      <c r="C118" s="154"/>
-      <c r="D118" s="154"/>
-      <c r="E118" s="154"/>
-    </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="154"/>
-      <c r="B119" s="154"/>
-      <c r="C119" s="154"/>
-      <c r="D119" s="154"/>
-      <c r="E119" s="154"/>
-    </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="154"/>
-      <c r="B120" s="154"/>
-      <c r="C120" s="154"/>
-      <c r="D120" s="154"/>
-      <c r="E120" s="154"/>
+      <c r="C114" s="45"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M115" s="8"/>
+    </row>
+    <row r="116" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="168"/>
+      <c r="B116" s="156"/>
+      <c r="C116" s="156"/>
+      <c r="D116" s="156"/>
+      <c r="E116" s="156"/>
+    </row>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="156"/>
+      <c r="B117" s="156"/>
+      <c r="C117" s="156"/>
+      <c r="D117" s="156"/>
+      <c r="E117" s="156"/>
+    </row>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="156"/>
+      <c r="B118" s="156"/>
+      <c r="C118" s="156"/>
+      <c r="D118" s="156"/>
+      <c r="E118" s="156"/>
+    </row>
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="156"/>
+      <c r="B119" s="156"/>
+      <c r="C119" s="156"/>
+      <c r="D119" s="156"/>
+      <c r="E119" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A86:E88"/>
+    <mergeCell ref="A110:C111"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A71:B72"/>
+    <mergeCell ref="A116:E119"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="E71:E72"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A87:E89"/>
-    <mergeCell ref="A111:C112"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A72:B73"/>
-    <mergeCell ref="A117:E120"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2945,30 +2933,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2976,21 +2964,21 @@
         <v>60</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="185" t="s">
+      <c r="F1" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3010,14 +2998,14 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="179">
+      <c r="O2" s="182">
         <f>T4</f>
         <v>3000000</v>
       </c>
-      <c r="P2" s="154"/>
+      <c r="P2" s="156"/>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3036,59 +3024,59 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="183">
+      <c r="O3" s="186">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="184"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="173" t="s">
+      <c r="P3" s="187"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="180" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="183" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="175" t="s">
+      <c r="C4" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="175" t="s">
+      <c r="D4" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="176" t="s">
+      <c r="E4" s="175" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="175" t="s">
+      <c r="F4" s="173" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="175" t="s">
+      <c r="G4" s="173" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="175" t="s">
+      <c r="H4" s="173" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="176" t="s">
+      <c r="I4" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="186" t="s">
+      <c r="J4" s="178" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="178" t="s">
+      <c r="K4" s="181" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="187" t="s">
+      <c r="L4" s="179" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="178" t="s">
+      <c r="M4" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="178" t="s">
+      <c r="N4" s="181" t="s">
         <v>78</v>
       </c>
       <c r="O4" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="182" t="s">
+      <c r="P4" s="185" t="s">
         <v>80</v>
       </c>
       <c r="S4" s="43"/>
@@ -3096,28 +3084,28 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="174"/>
-      <c r="B5" s="181"/>
+      <c r="B5" s="184"/>
       <c r="C5" s="174"/>
       <c r="D5" s="174"/>
-      <c r="E5" s="177"/>
+      <c r="E5" s="176"/>
       <c r="F5" s="174"/>
       <c r="G5" s="174"/>
       <c r="H5" s="174"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
       <c r="L5" s="174"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="177"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="176"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 14/08</v>
+        <v>VTO 15/09</v>
       </c>
       <c r="P5" s="174"/>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>81</v>
       </c>
@@ -3180,7 +3168,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
@@ -3241,7 +3229,7 @@
       </c>
       <c r="R7" s="43"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>85</v>
       </c>
@@ -3301,7 +3289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>92</v>
       </c>
@@ -3362,7 +3350,7 @@
       </c>
       <c r="S9" s="43"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>92</v>
       </c>
@@ -3420,7 +3408,7 @@
       </c>
       <c r="S10" s="43"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>99</v>
       </c>
@@ -3478,7 +3466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>99</v>
       </c>
@@ -3538,7 +3526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>105</v>
       </c>
@@ -3600,7 +3588,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>105</v>
       </c>
@@ -3660,7 +3648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>113</v>
       </c>
@@ -3718,7 +3706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>113</v>
       </c>
@@ -3778,7 +3766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>119</v>
       </c>
@@ -3835,7 +3823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>119</v>
       </c>
@@ -3894,7 +3882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>125</v>
       </c>
@@ -3949,7 +3937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>125</v>
       </c>
@@ -4012,7 +4000,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>130</v>
       </c>
@@ -4070,7 +4058,7 @@
       </c>
       <c r="S21" s="42"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>130</v>
       </c>
@@ -4131,7 +4119,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>136</v>
       </c>
@@ -4145,7 +4133,7 @@
         <v>138</v>
       </c>
       <c r="E23" s="62" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F23" s="68">
         <v>5</v>
@@ -4188,7 +4176,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>136</v>
       </c>
@@ -4198,7 +4186,7 @@
       <c r="C24" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="188" t="s">
+      <c r="D24" s="153" t="s">
         <v>140</v>
       </c>
       <c r="E24" s="63"/>
@@ -4249,7 +4237,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
       <c r="D25" s="75"/>
@@ -4296,99 +4284,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
-      <c r="R26" s="189" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="161" t="s">
+      <c r="R26" s="154" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="168" t="s">
         <v>142</v>
       </c>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="154"/>
-      <c r="H28" s="154"/>
-      <c r="I28" s="154"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="154"/>
-      <c r="L28" s="154"/>
-      <c r="M28" s="154"/>
-      <c r="N28" s="154"/>
-      <c r="O28" s="154"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
-      <c r="K29" s="154"/>
-      <c r="L29" s="154"/>
-      <c r="M29" s="154"/>
-      <c r="N29" s="154"/>
-      <c r="O29" s="154"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="154"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="154"/>
-      <c r="I30" s="154"/>
-      <c r="J30" s="154"/>
-      <c r="K30" s="154"/>
-      <c r="L30" s="154"/>
-      <c r="M30" s="154"/>
-      <c r="N30" s="154"/>
-      <c r="O30" s="154"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="154"/>
-      <c r="J31" s="154"/>
-      <c r="K31" s="154"/>
-      <c r="L31" s="154"/>
-      <c r="M31" s="154"/>
-      <c r="N31" s="154"/>
-      <c r="O31" s="154"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="154"/>
-      <c r="I32" s="154"/>
-      <c r="J32" s="154"/>
-      <c r="K32" s="154"/>
-      <c r="L32" s="154"/>
-      <c r="M32" s="154"/>
-      <c r="N32" s="154"/>
-      <c r="O32" s="154"/>
-    </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="154"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="154"/>
-      <c r="H33" s="154"/>
-      <c r="I33" s="154"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="154"/>
-      <c r="N33" s="154"/>
-      <c r="O33" s="154"/>
+      <c r="E28" s="156"/>
+      <c r="F28" s="156"/>
+      <c r="G28" s="156"/>
+      <c r="H28" s="156"/>
+      <c r="I28" s="156"/>
+      <c r="J28" s="156"/>
+      <c r="K28" s="156"/>
+      <c r="L28" s="156"/>
+      <c r="M28" s="156"/>
+      <c r="N28" s="156"/>
+      <c r="O28" s="156"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="156"/>
+      <c r="H29" s="156"/>
+      <c r="I29" s="156"/>
+      <c r="J29" s="156"/>
+      <c r="K29" s="156"/>
+      <c r="L29" s="156"/>
+      <c r="M29" s="156"/>
+      <c r="N29" s="156"/>
+      <c r="O29" s="156"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="156"/>
+      <c r="G30" s="156"/>
+      <c r="H30" s="156"/>
+      <c r="I30" s="156"/>
+      <c r="J30" s="156"/>
+      <c r="K30" s="156"/>
+      <c r="L30" s="156"/>
+      <c r="M30" s="156"/>
+      <c r="N30" s="156"/>
+      <c r="O30" s="156"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="156"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="156"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="156"/>
+      <c r="O31" s="156"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="156"/>
+      <c r="G32" s="156"/>
+      <c r="H32" s="156"/>
+      <c r="I32" s="156"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="156"/>
+      <c r="L32" s="156"/>
+      <c r="M32" s="156"/>
+      <c r="N32" s="156"/>
+      <c r="O32" s="156"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="156"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="156"/>
+      <c r="I33" s="156"/>
+      <c r="J33" s="156"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="156"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>
@@ -4396,13 +4384,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4415,6 +4396,13 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/PUEYRREDON 1494/Agosto/PUEYRREDON Agosto.xlsx
+++ b/PUEYRREDON 1494/Agosto/PUEYRREDON Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F30F9A-99C5-4635-B878-3A53717CD1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AE874A-6422-4EB0-9A42-996059B91076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$114</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="164">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -87,9 +87,6 @@
     <t>HONORARIOS administracion RC</t>
   </si>
   <si>
-    <t>Mes de MAYO</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL </t>
   </si>
   <si>
@@ -462,57 +459,18 @@
     <t>Limpieza marquesina</t>
   </si>
   <si>
-    <t>METROGAS LO VENIMOS DIBUJANDO HACE 1 MES - HAY QUE ARREGLARLO</t>
-  </si>
-  <si>
     <t>DEPOSITA SIEMPRE VALERIA</t>
   </si>
   <si>
-    <t>Transf 17/07</t>
-  </si>
-  <si>
-    <t>Debito 14/07</t>
-  </si>
-  <si>
-    <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas - Se deben $500.000</t>
-  </si>
-  <si>
     <t>SUBIDOS EN JULI</t>
   </si>
   <si>
-    <t>PMC 28/07</t>
-  </si>
-  <si>
-    <t>Debito 30/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaffalon Veronica - Cambio de valvulas y adaptacion de cañeria bomba 1  </t>
-  </si>
-  <si>
-    <t>Transf 30/07</t>
-  </si>
-  <si>
-    <t>Servisur - cambio de luminarias (plafones, portalamparas, tubos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electricidad Leon - Materiales </t>
-  </si>
-  <si>
     <t xml:space="preserve">Punitorios mal cobrados </t>
   </si>
   <si>
-    <t xml:space="preserve">5/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
-  </si>
-  <si>
     <t>Lourdes</t>
   </si>
   <si>
-    <t>11/07 Transf no identificada - Valentina Cecilia Zarate</t>
-  </si>
-  <si>
-    <t>EL PAGO NO IDENTIFICADO DEL MES PASADO ES DE ELLA - RATON MARIELA</t>
-  </si>
-  <si>
     <t>VTO 15/09</t>
   </si>
   <si>
@@ -531,13 +489,34 @@
     <t>Transf 19/08</t>
   </si>
   <si>
-    <t>Transf 01/08</t>
-  </si>
-  <si>
     <t>Efect 02/08</t>
   </si>
   <si>
     <t>PMC 12/08</t>
+  </si>
+  <si>
+    <t>PMC 04/08</t>
+  </si>
+  <si>
+    <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas - Se debian $500.000</t>
+  </si>
+  <si>
+    <t>Transf 04/08</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
+  </si>
+  <si>
+    <t>Servisur - cambio de lamparas</t>
+  </si>
+  <si>
+    <t>Debito 26/08</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado del mes anterior</t>
   </si>
 </sst>
 </file>
@@ -545,14 +524,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;Bs&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="&quot;Bs&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -752,7 +731,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -819,12 +798,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1222,11 +1195,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1234,7 +1207,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1242,16 +1215,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1262,8 +1235,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1273,25 +1246,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1299,11 +1272,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,96 +1290,96 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1431,73 +1404,61 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1507,18 +1468,23 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1874,28 +1840,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M119"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M118"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="141"/>
       <c r="B1" s="142"/>
       <c r="C1" s="143"/>
       <c r="D1" s="143"/>
       <c r="E1" s="144"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="145"/>
       <c r="B2" s="137" t="s">
         <v>0</v>
@@ -1904,7 +1870,7 @@
       <c r="D2" s="137"/>
       <c r="E2" s="146"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="145"/>
       <c r="B3" s="137" t="s">
         <v>1</v>
@@ -1913,7 +1879,7 @@
       <c r="D3" s="137"/>
       <c r="E3" s="146"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="145"/>
       <c r="B4" s="138" t="s">
         <v>2</v>
@@ -1924,7 +1890,7 @@
       </c>
       <c r="E4" s="146"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="145" t="s">
         <v>4</v>
       </c>
@@ -1935,12 +1901,12 @@
       <c r="D5" s="136"/>
       <c r="E5" s="147"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="145" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="136" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C6" s="136"/>
       <c r="D6" s="137" t="s">
@@ -1948,7 +1914,7 @@
       </c>
       <c r="E6" s="147"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="148" t="s">
         <v>8</v>
       </c>
@@ -1957,60 +1923,60 @@
       <c r="D7" s="149"/>
       <c r="E7" s="150"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="155" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="156"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="156"/>
-      <c r="C10" s="156"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="165" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="154"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="154"/>
+      <c r="C10" s="154"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="133"/>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="159" t="s">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="156"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="156"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="156"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -2019,7 +1985,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>11</v>
       </c>
@@ -2028,41 +1994,41 @@
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="120">
-        <v>612874.4</v>
+        <v>798601.4</v>
       </c>
       <c r="E23" s="80"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="120">
-        <v>-143013.39000000001</v>
+        <v>-174514.13</v>
       </c>
       <c r="E24" s="80"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="120">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="E25" s="80"/>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2070,7 +2036,7 @@
       <c r="E26" s="80"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
         <v>15</v>
       </c>
@@ -2078,12 +2044,12 @@
       <c r="C27" s="57"/>
       <c r="D27" s="121">
         <f>SUM(D23:D26)</f>
-        <v>469862</v>
+        <v>624088</v>
       </c>
       <c r="E27" s="81"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2091,7 +2057,7 @@
       <c r="E28" s="80"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2099,7 +2065,7 @@
       <c r="E29" s="80"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="57" t="s">
         <v>15</v>
       </c>
@@ -2111,7 +2077,7 @@
       </c>
       <c r="E30" s="81"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>16</v>
       </c>
@@ -2120,11 +2086,11 @@
       <c r="D31" s="122"/>
       <c r="E31" s="82">
         <f>D27+D30</f>
-        <v>469862</v>
+        <v>624088</v>
       </c>
       <c r="F31" s="15"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="32" t="s">
         <v>17</v>
       </c>
@@ -2133,25 +2099,25 @@
       <c r="D32" s="123"/>
       <c r="E32" s="83"/>
     </row>
-    <row r="33" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="191">
+      <c r="D33" s="120">
         <v>35000</v>
       </c>
       <c r="E33" s="84"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="120">
@@ -2159,12 +2125,12 @@
       </c>
       <c r="E34" s="84"/>
       <c r="H34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
@@ -2174,40 +2140,40 @@
         <v>170100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="125"/>
       <c r="E36" s="66"/>
     </row>
-    <row r="37" spans="1:8" s="36" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="160" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="158"/>
+    <row r="37" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="167" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="157"/>
       <c r="C37" s="55"/>
       <c r="D37" s="126">
         <v>87562.7</v>
       </c>
       <c r="E37" s="106"/>
     </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="160" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="158"/>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="167" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="157"/>
       <c r="C38" s="55"/>
       <c r="D38" s="127">
         <v>6646.91</v>
       </c>
       <c r="E38" s="106"/>
     </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -2217,81 +2183,81 @@
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="128"/>
       <c r="E40" s="87"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="53"/>
-      <c r="D41" s="188">
+      <c r="D41" s="127">
         <v>380468.13</v>
       </c>
       <c r="E41" s="107" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="G41" s="104"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="188">
+      <c r="D42" s="127">
         <v>19706.62</v>
       </c>
       <c r="E42" s="108" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="188">
+      <c r="D43" s="127">
         <v>63551.19</v>
       </c>
       <c r="E43" s="108" t="str">
         <f>E42</f>
-        <v>Debito 14/07</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="188">
+      <c r="D44" s="127">
         <v>3941.32</v>
       </c>
       <c r="E44" s="109" t="str">
         <f>E43</f>
-        <v>Debito 14/07</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="24"/>
@@ -2301,628 +2267,603 @@
         <v>467667.26</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="24"/>
       <c r="D46" s="128"/>
       <c r="E46" s="87"/>
     </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="53" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="188">
+      <c r="D47" s="127">
         <v>44625</v>
       </c>
       <c r="E47" s="90" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G47" s="112"/>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="127">
-        <v>86610.08</v>
+        <f>180470.49-86610.08</f>
+        <v>93860.409999999989</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="127">
-        <v>25000</v>
+        <v>23426.2</v>
       </c>
       <c r="E49" s="90" t="s">
-        <v>151</v>
-      </c>
-      <c r="G49" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="189" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="127">
+        <v>30000</v>
+      </c>
+      <c r="E50" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="190"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="188">
-        <v>135000</v>
-      </c>
-      <c r="E50" s="90" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="127">
-        <v>119000</v>
+        <v>30000</v>
       </c>
       <c r="E51" s="90" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B52" s="5"/>
+    <row r="52" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="168" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" s="169"/>
       <c r="C52" s="5"/>
       <c r="D52" s="127">
-        <v>35626.879999999997</v>
+        <v>500000</v>
       </c>
       <c r="E52" s="90" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="188">
-        <v>30000</v>
-      </c>
-      <c r="E53" s="90" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="161" t="s">
-        <v>149</v>
-      </c>
-      <c r="B54" s="162"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="127">
-        <v>500000</v>
-      </c>
-      <c r="E54" s="90"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="157" t="s">
-        <v>143</v>
-      </c>
-      <c r="B55" s="158"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="152">
-        <v>67030</v>
-      </c>
-      <c r="E55" s="108" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="156" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" s="157"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="152"/>
+      <c r="E53" s="108"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="124"/>
+      <c r="E54" s="86">
+        <f>SUM(D47:D53)</f>
+        <v>721911.61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="124"/>
-      <c r="E56" s="86">
-        <f>SUM(D47:D55)</f>
-        <v>1042891.96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="32" t="s">
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="124"/>
+      <c r="E55" s="89"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="53"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="88"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="124"/>
-      <c r="E57" s="89"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="53"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="88"/>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="23" t="s">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="92">
+        <f>SUM(D56:D56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="92">
-        <f>SUM(D58:D58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="32" t="s">
+      <c r="B58" s="65"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="122"/>
+      <c r="E58" s="89"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="127">
+        <v>45769.760000000002</v>
+      </c>
+      <c r="E59" s="93"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="65"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="122"/>
-      <c r="E60" s="89"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="127">
-        <v>48482.26</v>
-      </c>
-      <c r="E61" s="93"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="127">
+        <v>56000</v>
+      </c>
+      <c r="E60" s="91"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="94"/>
+      <c r="E61" s="86">
+        <f>SUM(D59:D60)</f>
+        <v>101769.76000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="127">
-        <v>49082</v>
-      </c>
-      <c r="E62" s="91"/>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="B63" s="52"/>
-      <c r="C63" s="52"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="86">
-        <f>SUM(D61:D62)</f>
-        <v>97564.260000000009</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="80"/>
-      <c r="E64" s="95"/>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="25" t="s">
+      <c r="D62" s="80"/>
+      <c r="E62" s="95"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="96"/>
+      <c r="E63" s="97">
+        <f>3200000-2179746.24</f>
+        <v>1020253.7599999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="D64" s="98"/>
+      <c r="E64" s="99"/>
+      <c r="F64" s="43"/>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="96"/>
-      <c r="E65" s="97">
-        <v>529019.43999999994</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="100"/>
+      <c r="E65" s="101">
+        <f>(SUM(E31:E63))</f>
+        <v>3200000</v>
+      </c>
+      <c r="F65" s="43"/>
+      <c r="G65" s="112"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D66" s="98"/>
-      <c r="E66" s="99"/>
-      <c r="F66" s="43"/>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
+      <c r="E66" s="98"/>
+      <c r="G66" s="112"/>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="98"/>
+      <c r="E67" s="98"/>
+    </row>
+    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="100"/>
-      <c r="E67" s="101">
-        <f>(SUM(E31:E65))</f>
-        <v>2871314.53</v>
-      </c>
-      <c r="F67" s="43"/>
-      <c r="G67" s="112"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D68" s="98"/>
-      <c r="E68" s="98"/>
-      <c r="G68" s="112"/>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D69" s="98"/>
-      <c r="E69" s="98"/>
-    </row>
-    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="102"/>
+      <c r="E68" s="103"/>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="156" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="158"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="162">
+        <v>181000</v>
+      </c>
+      <c r="E69" s="163"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="159"/>
+      <c r="B70" s="160"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="187"/>
+      <c r="E70" s="164"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="156"/>
+      <c r="B71" s="157"/>
+      <c r="C71" s="53"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="131"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="50"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="188">
+        <f>SUM(D69:D71)</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="102"/>
-      <c r="E70" s="103"/>
-    </row>
-    <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="157" t="s">
-        <v>158</v>
-      </c>
-      <c r="B71" s="165"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="169">
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="113"/>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="67">
+        <f>E72+E74</f>
         <v>181000</v>
       </c>
-      <c r="E71" s="171"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="166"/>
-      <c r="B72" s="167"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="170"/>
-      <c r="E72" s="172"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="157"/>
-      <c r="B73" s="158"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="131"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="50"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58">
-        <f>SUM(D71:D73)</f>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" s="79">
+        <f>E65</f>
+        <v>3200000</v>
+      </c>
+      <c r="D78" s="43"/>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="B79" s="79">
+        <f>E65-E63</f>
+        <v>2179746.2400000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" s="79">
+        <f>E76-E74</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="113"/>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="67">
-        <f>E74+E76</f>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="78" t="s">
+        <v>47</v>
+      </c>
+      <c r="B81" s="79">
+        <f>E76</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="79">
-        <f>E67</f>
-        <v>2871314.53</v>
-      </c>
-      <c r="D80" s="43"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="78" t="s">
-        <v>46</v>
-      </c>
-      <c r="B81" s="79">
-        <f>E67-E65</f>
-        <v>2342295.09</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="B82" s="79">
-        <f>E78-E76</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="78" t="s">
+    <row r="82" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="153"/>
+      <c r="B84" s="154"/>
+      <c r="C84" s="154"/>
+      <c r="D84" s="154"/>
+      <c r="E84" s="154"/>
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="154"/>
+      <c r="B85" s="154"/>
+      <c r="C85" s="154"/>
+      <c r="D85" s="154"/>
+      <c r="E85" s="154"/>
+    </row>
+    <row r="86" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="154"/>
+      <c r="B86" s="154"/>
+      <c r="C86" s="154"/>
+      <c r="D86" s="154"/>
+      <c r="E86" s="154"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B83" s="79">
-        <f>E78</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="163"/>
-      <c r="B86" s="156"/>
-      <c r="C86" s="156"/>
-      <c r="D86" s="156"/>
-      <c r="E86" s="156"/>
-    </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="156"/>
-      <c r="B87" s="156"/>
-      <c r="C87" s="156"/>
-      <c r="D87" s="156"/>
-      <c r="E87" s="156"/>
-    </row>
-    <row r="88" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="156"/>
-      <c r="B88" s="156"/>
-      <c r="C88" s="156"/>
-      <c r="D88" s="156"/>
-      <c r="E88" s="156"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="16" t="s">
+      <c r="B88" s="38"/>
+      <c r="C88" s="17"/>
+    </row>
+    <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B90" s="38"/>
+      <c r="B89" s="111">
+        <v>-705431.13749999925</v>
+      </c>
+      <c r="C89" s="19"/>
+    </row>
+    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B90" s="39">
+        <f>PRORRATEO!H25</f>
+        <v>2907739.07</v>
+      </c>
       <c r="C90" s="17"/>
     </row>
-    <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B91" s="111">
-        <v>-1000157.7574999998</v>
-      </c>
-      <c r="C91" s="19"/>
-    </row>
-    <row r="92" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="18" t="s">
+    <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B92" s="39">
-        <f>PRORRATEO!H25</f>
-        <v>2893536.18</v>
+      <c r="B91" s="47"/>
+      <c r="C91" s="17"/>
+    </row>
+    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="151" t="s">
+        <v>146</v>
+      </c>
+      <c r="B92" s="47">
+        <v>-946</v>
       </c>
       <c r="C92" s="17"/>
     </row>
-    <row r="93" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="18" t="s">
+    <row r="93" spans="1:5" s="185" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="151" t="s">
+        <v>163</v>
+      </c>
+      <c r="B93" s="47">
+        <v>-262000</v>
+      </c>
+      <c r="C93" s="17"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B93" s="47"/>
-      <c r="C93" s="17"/>
-    </row>
-    <row r="94" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="151" t="s">
-        <v>157</v>
-      </c>
-      <c r="B94" s="47">
-        <v>-8829</v>
+      <c r="B94" s="91">
+        <f>B113</f>
+        <v>0</v>
       </c>
       <c r="C94" s="17"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="18" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B95" s="91">
-        <f>B114</f>
-        <v>262000</v>
+      <c r="B95" s="47">
+        <f>-B79</f>
+        <v>-2179746.2400000002</v>
       </c>
       <c r="C95" s="17"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="37" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="21" t="s">
         <v>54</v>
       </c>
       <c r="B96" s="47">
-        <f>-B81</f>
-        <v>-2342295.09</v>
+        <f>-(B80)</f>
+        <v>-181000</v>
       </c>
       <c r="C96" s="17"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="21" t="s">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="110">
+        <f>SUM(B89:B96)</f>
+        <v>-421384.30749999965</v>
+      </c>
+      <c r="C97" s="20"/>
+    </row>
+    <row r="98" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="40"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="43"/>
+    </row>
+    <row r="99" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="41"/>
+      <c r="C99" s="20"/>
+    </row>
+    <row r="100" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="40"/>
+      <c r="C100" s="35"/>
+    </row>
+    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B97" s="47">
-        <f>-(B82)</f>
-        <v>-181000</v>
-      </c>
-      <c r="C97" s="17"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B98" s="110">
-        <f>SUM(B91:B97)</f>
-        <v>-376745.66749999952</v>
-      </c>
-      <c r="C98" s="20"/>
-    </row>
-    <row r="99" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="40"/>
-      <c r="C99" s="20"/>
-      <c r="D99" s="43"/>
-    </row>
-    <row r="100" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="41"/>
-      <c r="C100" s="20"/>
-    </row>
-    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="40"/>
+      <c r="B101" s="33"/>
       <c r="C101" s="35"/>
-    </row>
-    <row r="102" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="29" t="s">
+      <c r="D101" s="46"/>
+    </row>
+    <row r="102" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B102" s="34">
+        <v>0</v>
+      </c>
+      <c r="C102" s="35"/>
+    </row>
+    <row r="103" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B102" s="33"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="46"/>
-    </row>
-    <row r="103" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B103" s="34">
+      <c r="B103" s="33">
         <v>0</v>
       </c>
-      <c r="C103" s="35"/>
-    </row>
-    <row r="104" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="20"/>
+      <c r="D103" s="43"/>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B104" s="33">
         <v>0</v>
       </c>
       <c r="C104" s="20"/>
-      <c r="D104" s="43"/>
-    </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B105" s="33">
         <v>0</v>
       </c>
-      <c r="C105" s="20"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B106" s="33">
+      <c r="C105" s="22"/>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B106" s="48">
+        <f>SUM(B102:B105)</f>
         <v>0</v>
       </c>
-      <c r="C106" s="22"/>
-    </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="29" t="s">
+      <c r="C106" s="17"/>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="155" t="s">
         <v>58</v>
       </c>
-      <c r="B107" s="48">
-        <f>SUM(B103:B106)</f>
+      <c r="B109" s="154"/>
+      <c r="C109" s="154"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="154"/>
+      <c r="B110" s="154"/>
+      <c r="C110" s="154"/>
+    </row>
+    <row r="111" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="55"/>
+      <c r="B111" s="33"/>
+      <c r="C111" s="33">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="55"/>
+      <c r="B112" s="33"/>
+      <c r="C112" s="40"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B113" s="105">
+        <f>SUM(B111:B112)</f>
         <v>0</v>
       </c>
-      <c r="C107" s="17"/>
-    </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="164" t="s">
-        <v>59</v>
-      </c>
-      <c r="B110" s="156"/>
-      <c r="C110" s="156"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="156"/>
-      <c r="B111" s="156"/>
-      <c r="C111" s="156"/>
-    </row>
-    <row r="112" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="B112" s="33">
-        <v>262000</v>
-      </c>
-      <c r="C112" s="33">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="55"/>
-      <c r="B113" s="33"/>
-      <c r="C113" s="40"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B114" s="105">
-        <f>SUM(B112:B113)</f>
-        <v>262000</v>
-      </c>
-      <c r="C114" s="45"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M115" s="8"/>
-    </row>
-    <row r="116" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="168"/>
-      <c r="B116" s="156"/>
-      <c r="C116" s="156"/>
-      <c r="D116" s="156"/>
-      <c r="E116" s="156"/>
-    </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="156"/>
-      <c r="B117" s="156"/>
-      <c r="C117" s="156"/>
-      <c r="D117" s="156"/>
-      <c r="E117" s="156"/>
-    </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="156"/>
-      <c r="B118" s="156"/>
-      <c r="C118" s="156"/>
-      <c r="D118" s="156"/>
-      <c r="E118" s="156"/>
-    </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="156"/>
-      <c r="B119" s="156"/>
-      <c r="C119" s="156"/>
-      <c r="D119" s="156"/>
-      <c r="E119" s="156"/>
+      <c r="C113" s="45"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M114" s="8"/>
+    </row>
+    <row r="115" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="161"/>
+      <c r="B115" s="154"/>
+      <c r="C115" s="154"/>
+      <c r="D115" s="154"/>
+      <c r="E115" s="154"/>
+    </row>
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="154"/>
+      <c r="B116" s="154"/>
+      <c r="C116" s="154"/>
+      <c r="D116" s="154"/>
+      <c r="E116" s="154"/>
+    </row>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="154"/>
+      <c r="B117" s="154"/>
+      <c r="C117" s="154"/>
+      <c r="D117" s="154"/>
+      <c r="E117" s="154"/>
+    </row>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="154"/>
+      <c r="B118" s="154"/>
+      <c r="C118" s="154"/>
+      <c r="D118" s="154"/>
+      <c r="E118" s="154"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A86:E88"/>
-    <mergeCell ref="A110:C111"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A71:B72"/>
-    <mergeCell ref="A116:E119"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="E71:E72"/>
+  <mergeCells count="13">
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A84:E86"/>
+    <mergeCell ref="A109:C110"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A69:B70"/>
+    <mergeCell ref="A115:E118"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2933,52 +2874,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" customWidth="1"/>
-    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="182" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="177" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="154"/>
+      <c r="O1" s="154"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2994,23 +2935,23 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="182">
+      <c r="O2" s="176">
         <f>T4</f>
-        <v>3000000</v>
-      </c>
-      <c r="P2" s="156"/>
+        <v>3200000</v>
+      </c>
+      <c r="P2" s="154"/>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -3020,106 +2961,106 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="186">
+      <c r="O3" s="180">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="187"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="180" t="s">
+      <c r="P3" s="181"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="170" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="177" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="183" t="s">
+      <c r="C4" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="D4" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="173" t="s">
+      <c r="E4" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="175" t="s">
+      <c r="F4" s="172" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="173" t="s">
+      <c r="G4" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="173" t="s">
+      <c r="H4" s="172" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="I4" s="173" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="175" t="s">
+      <c r="J4" s="183" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="K4" s="175" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="181" t="s">
+      <c r="L4" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="M4" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="181" t="s">
+      <c r="N4" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="O4" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="O4" s="61" t="s">
+      <c r="P4" s="179" t="s">
         <v>79</v>
-      </c>
-      <c r="P4" s="185" t="s">
-        <v>80</v>
       </c>
       <c r="S4" s="43"/>
       <c r="T4">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="174"/>
-      <c r="B5" s="184"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="176"/>
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="171"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="174"/>
+      <c r="K5" s="174"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="174"/>
+      <c r="N5" s="174"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="P5" s="174"/>
-    </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="171"/>
+    </row>
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="62">
         <v>1</v>
       </c>
       <c r="C6" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="E6" s="62" t="s">
         <v>83</v>
-      </c>
-      <c r="E6" s="62" t="s">
-        <v>84</v>
       </c>
       <c r="F6" s="68">
         <v>3</v>
@@ -3146,19 +3087,19 @@
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6:M24" si="3">O$2*F6%</f>
-        <v>90000</v>
+        <v>96000</v>
       </c>
       <c r="N6" s="114">
         <f t="shared" ref="N6:N24" si="4">SUM(J6:M6)</f>
-        <v>95430</v>
+        <v>101430</v>
       </c>
       <c r="O6" s="118" t="str">
         <f t="shared" ref="O6:O24" si="5">CONCATENATE("$",ROUND(N6,0), ",", Q6)</f>
-        <v>$95430,1</v>
+        <v>$101430,1</v>
       </c>
       <c r="P6" s="119" t="str">
         <f t="shared" ref="P6:P24" si="6">CONCATENATE("$",ROUND(N6*3%+ N6,0), ",", Q6)</f>
-        <v>$98293,1</v>
+        <v>$104473,1</v>
       </c>
       <c r="Q6" s="43" t="str">
         <f t="shared" ref="Q6:Q24" si="7">CONCATENATE(B6)</f>
@@ -3168,31 +3109,31 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="62">
         <v>2</v>
       </c>
       <c r="C7" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="E7" s="62" t="s">
         <v>87</v>
-      </c>
-      <c r="E7" s="62" t="s">
-        <v>88</v>
       </c>
       <c r="F7" s="68">
         <v>3.8</v>
       </c>
       <c r="G7" s="134">
-        <v>117849.2</v>
+        <v>120878.2</v>
       </c>
       <c r="H7" s="130">
         <f>G7</f>
-        <v>117849.2</v>
+        <v>120878.2</v>
       </c>
       <c r="I7" s="70"/>
       <c r="J7" s="117">
@@ -3209,19 +3150,19 @@
       </c>
       <c r="M7" s="72">
         <f t="shared" si="3"/>
-        <v>114000</v>
+        <v>121600</v>
       </c>
       <c r="N7" s="114">
         <f t="shared" si="4"/>
-        <v>120878</v>
+        <v>128478</v>
       </c>
       <c r="O7" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$120878,2</v>
+        <v>$128478,2</v>
       </c>
       <c r="P7" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$124504,2</v>
+        <v>$132332,2</v>
       </c>
       <c r="Q7" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3229,40 +3170,37 @@
       </c>
       <c r="R7" s="43"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="62">
         <v>3</v>
       </c>
       <c r="C8" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="E8" s="62" t="s">
         <v>90</v>
-      </c>
-      <c r="E8" s="62" t="s">
-        <v>91</v>
       </c>
       <c r="F8" s="68">
         <v>3</v>
       </c>
       <c r="G8" s="134">
-        <v>98293.3</v>
-      </c>
-      <c r="H8" s="130">
-        <f>G8</f>
-        <v>98293.3</v>
-      </c>
+        <v>95430.3</v>
+      </c>
+      <c r="H8" s="130"/>
       <c r="I8" s="70"/>
       <c r="J8" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>95430.3</v>
       </c>
       <c r="K8" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4771.5150000000003</v>
       </c>
       <c r="L8" s="72">
         <f t="shared" si="2"/>
@@ -3270,59 +3208,56 @@
       </c>
       <c r="M8" s="72">
         <f t="shared" si="3"/>
-        <v>90000</v>
+        <v>96000</v>
       </c>
       <c r="N8" s="114">
         <f t="shared" si="4"/>
-        <v>95430</v>
+        <v>201631.815</v>
       </c>
       <c r="O8" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$95430,3</v>
+        <v>$201632,3</v>
       </c>
       <c r="P8" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$98293,3</v>
+        <v>$207681,3</v>
       </c>
       <c r="Q8" s="43" t="str">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="62">
         <v>4</v>
       </c>
       <c r="C9" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="E9" s="62" t="s">
         <v>94</v>
-      </c>
-      <c r="E9" s="62" t="s">
-        <v>95</v>
       </c>
       <c r="F9" s="68">
         <v>3.1</v>
       </c>
       <c r="G9" s="134">
-        <v>270048.03999999998</v>
-      </c>
-      <c r="H9" s="130">
-        <f>G9</f>
-        <v>270048.03999999998</v>
-      </c>
+        <v>98611.4</v>
+      </c>
+      <c r="H9" s="130"/>
       <c r="I9" s="70"/>
       <c r="J9" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>98611.4</v>
       </c>
       <c r="K9" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4930.57</v>
       </c>
       <c r="L9" s="72">
         <f t="shared" si="2"/>
@@ -3330,19 +3265,19 @@
       </c>
       <c r="M9" s="72">
         <f t="shared" si="3"/>
-        <v>93000</v>
+        <v>99200</v>
       </c>
       <c r="N9" s="114">
         <f t="shared" si="4"/>
-        <v>98611</v>
+        <v>208352.97</v>
       </c>
       <c r="O9" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$98611,4</v>
+        <v>$208353,4</v>
       </c>
       <c r="P9" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$101569,4</v>
+        <v>$214604,4</v>
       </c>
       <c r="Q9" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3350,37 +3285,37 @@
       </c>
       <c r="S9" s="43"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" s="62">
         <v>5</v>
       </c>
       <c r="C10" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="E10" s="62" t="s">
         <v>97</v>
-      </c>
-      <c r="E10" s="62" t="s">
-        <v>98</v>
       </c>
       <c r="F10" s="68">
         <v>3.1</v>
       </c>
       <c r="G10" s="134">
-        <v>98611.5</v>
+        <v>202153.5</v>
       </c>
       <c r="H10" s="130"/>
       <c r="I10" s="70"/>
       <c r="J10" s="117">
         <f t="shared" si="0"/>
-        <v>98611.5</v>
+        <v>202153.5</v>
       </c>
       <c r="K10" s="71">
         <f t="shared" si="1"/>
-        <v>4930.5750000000007</v>
+        <v>10107.675000000001</v>
       </c>
       <c r="L10" s="72">
         <f t="shared" si="2"/>
@@ -3388,19 +3323,19 @@
       </c>
       <c r="M10" s="72">
         <f t="shared" si="3"/>
-        <v>93000</v>
+        <v>99200</v>
       </c>
       <c r="N10" s="114">
         <f t="shared" si="4"/>
-        <v>202153.07500000001</v>
+        <v>317072.17499999999</v>
       </c>
       <c r="O10" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$202153,5</v>
+        <v>$317072,5</v>
       </c>
       <c r="P10" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$208218,5</v>
+        <v>$326584,5</v>
       </c>
       <c r="Q10" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3408,18 +3343,18 @@
       </c>
       <c r="S10" s="43"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" s="62">
         <v>6</v>
       </c>
       <c r="C11" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="62" t="s">
         <v>100</v>
-      </c>
-      <c r="D11" s="62" t="s">
-        <v>101</v>
       </c>
       <c r="E11" s="62"/>
       <c r="F11" s="68">
@@ -3447,50 +3382,50 @@
       </c>
       <c r="M11" s="72">
         <f t="shared" si="3"/>
-        <v>96000</v>
+        <v>102400</v>
       </c>
       <c r="N11" s="114">
         <f t="shared" si="4"/>
-        <v>101792</v>
+        <v>108192</v>
       </c>
       <c r="O11" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$101792,6</v>
+        <v>$108192,6</v>
       </c>
       <c r="P11" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$104846,6</v>
+        <v>$111438,6</v>
       </c>
       <c r="Q11" s="43" t="str">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B12" s="62">
         <v>7</v>
       </c>
       <c r="C12" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="E12" s="62" t="s">
         <v>103</v>
-      </c>
-      <c r="E12" s="62" t="s">
-        <v>104</v>
       </c>
       <c r="F12" s="68">
         <v>3.3</v>
       </c>
       <c r="G12" s="134">
-        <v>102343.7</v>
+        <v>104973.7</v>
       </c>
       <c r="H12" s="130">
         <f>G12</f>
-        <v>102343.7</v>
+        <v>104973.7</v>
       </c>
       <c r="I12" s="70"/>
       <c r="J12" s="117">
@@ -3507,58 +3442,59 @@
       </c>
       <c r="M12" s="72">
         <f t="shared" si="3"/>
-        <v>99000</v>
+        <v>105600</v>
       </c>
       <c r="N12" s="114">
         <f t="shared" si="4"/>
-        <v>104973</v>
+        <v>111573</v>
       </c>
       <c r="O12" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$104973,7</v>
+        <v>$111573,7</v>
       </c>
       <c r="P12" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$108122,7</v>
+        <v>$114920,7</v>
       </c>
       <c r="Q12" s="43" t="str">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="62">
         <v>23</v>
       </c>
       <c r="C13" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="62" t="s">
+      <c r="E13" s="62" t="s">
         <v>107</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>108</v>
       </c>
       <c r="F13" s="68">
         <v>6.3</v>
       </c>
       <c r="G13" s="134">
-        <v>200403.23</v>
+        <v>212376.23</v>
       </c>
       <c r="H13" s="69">
-        <v>189000</v>
+        <f>189000+23976.23</f>
+        <v>212976.23</v>
       </c>
       <c r="I13" s="70"/>
       <c r="J13" s="117">
         <f t="shared" si="0"/>
-        <v>11403.23000000001</v>
+        <v>-600</v>
       </c>
       <c r="K13" s="71">
         <f t="shared" si="1"/>
-        <v>570.1615000000005</v>
+        <v>0</v>
       </c>
       <c r="L13" s="72">
         <f t="shared" si="2"/>
@@ -3566,43 +3502,43 @@
       </c>
       <c r="M13" s="72">
         <f t="shared" si="3"/>
-        <v>189000</v>
+        <v>201600</v>
       </c>
       <c r="N13" s="114">
         <f t="shared" si="4"/>
-        <v>212376.39150000003</v>
+        <v>212403</v>
       </c>
       <c r="O13" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$212376,23</v>
+        <v>$212403,23</v>
       </c>
       <c r="P13" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$218748,23</v>
+        <v>$218775,23</v>
       </c>
       <c r="Q13" s="43" t="str">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="62">
         <v>22</v>
       </c>
       <c r="C14" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="62" t="s">
+      <c r="E14" s="62" t="s">
         <v>111</v>
-      </c>
-      <c r="E14" s="62" t="s">
-        <v>112</v>
       </c>
       <c r="F14" s="68">
         <v>5.0999999999999996</v>
@@ -3629,53 +3565,52 @@
       </c>
       <c r="M14" s="72">
         <f t="shared" si="3"/>
-        <v>153000</v>
+        <v>163200</v>
       </c>
       <c r="N14" s="114">
         <f t="shared" si="4"/>
-        <v>162231</v>
+        <v>172431</v>
       </c>
       <c r="O14" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$162231,22</v>
+        <v>$172431,22</v>
       </c>
       <c r="P14" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$167098,22</v>
+        <v>$177604,22</v>
       </c>
       <c r="Q14" s="43" t="str">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" s="62">
         <v>21</v>
       </c>
       <c r="C15" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="62" t="s">
         <v>114</v>
-      </c>
-      <c r="D15" s="62" t="s">
-        <v>115</v>
       </c>
       <c r="E15" s="63"/>
       <c r="F15" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G15" s="134">
-        <v>264918.21000000002</v>
+        <v>260842.21</v>
       </c>
       <c r="H15" s="69">
-        <f>G15</f>
-        <v>264918.21000000002</v>
+        <v>268667.21000000002</v>
       </c>
       <c r="I15" s="70"/>
       <c r="J15" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7825.0000000000291</v>
       </c>
       <c r="K15" s="71">
         <f t="shared" si="1"/>
@@ -3687,40 +3622,40 @@
       </c>
       <c r="M15" s="72">
         <f t="shared" si="3"/>
-        <v>245999.99999999997</v>
+        <v>262399.99999999994</v>
       </c>
       <c r="N15" s="114">
         <f t="shared" si="4"/>
-        <v>260841.99999999997</v>
+        <v>269416.99999999988</v>
       </c>
       <c r="O15" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$260842,21</v>
+        <v>$269417,21</v>
       </c>
       <c r="P15" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$268667,21</v>
+        <v>$277500,21</v>
       </c>
       <c r="Q15" s="43" t="str">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B16" s="62">
         <v>14</v>
       </c>
       <c r="C16" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="62" t="s">
+      <c r="E16" s="62" t="s">
         <v>117</v>
-      </c>
-      <c r="E16" s="62" t="s">
-        <v>118</v>
       </c>
       <c r="F16" s="68">
         <v>6.1</v>
@@ -3747,52 +3682,52 @@
       </c>
       <c r="M16" s="72">
         <f t="shared" si="3"/>
-        <v>183000</v>
+        <v>195200</v>
       </c>
       <c r="N16" s="114">
         <f t="shared" si="4"/>
-        <v>194041</v>
+        <v>206241</v>
       </c>
       <c r="O16" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$194041,14</v>
+        <v>$206241,14</v>
       </c>
       <c r="P16" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$199862,14</v>
+        <v>$212428,14</v>
       </c>
       <c r="Q16" s="43" t="str">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="62">
         <v>13</v>
       </c>
       <c r="C17" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="62" t="s">
         <v>120</v>
-      </c>
-      <c r="D17" s="62" t="s">
-        <v>121</v>
       </c>
       <c r="E17" s="63"/>
       <c r="F17" s="68">
         <v>5</v>
       </c>
       <c r="G17" s="134">
-        <v>155065.13</v>
+        <v>154398.13</v>
       </c>
       <c r="H17" s="69">
-        <v>159717.13</v>
+        <v>159030.13</v>
       </c>
       <c r="I17" s="70"/>
       <c r="J17" s="117">
         <f t="shared" si="0"/>
-        <v>-4652</v>
+        <v>-4632</v>
       </c>
       <c r="K17" s="71">
         <f t="shared" si="1"/>
@@ -3804,46 +3739,46 @@
       </c>
       <c r="M17" s="72">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="N17" s="114">
         <f t="shared" si="4"/>
-        <v>154398</v>
+        <v>164418</v>
       </c>
       <c r="O17" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$154398,13</v>
+        <v>$164418,13</v>
       </c>
       <c r="P17" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$159030,13</v>
+        <v>$169351,13</v>
       </c>
       <c r="Q17" s="43" t="str">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B18" s="62">
         <v>12</v>
       </c>
       <c r="C18" s="62" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="62" t="s">
+      <c r="E18" s="62" t="s">
         <v>123</v>
-      </c>
-      <c r="E18" s="62" t="s">
-        <v>124</v>
       </c>
       <c r="F18" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G18" s="134">
-        <v>14360927.119999999</v>
+        <v>15065931.119999999</v>
       </c>
       <c r="H18" s="69">
         <v>260842</v>
@@ -3851,11 +3786,11 @@
       <c r="I18" s="70"/>
       <c r="J18" s="117">
         <f t="shared" si="0"/>
-        <v>14100085.119999999</v>
+        <v>14805089.119999999</v>
       </c>
       <c r="K18" s="71">
         <f t="shared" si="1"/>
-        <v>705004.25600000005</v>
+        <v>740254.45600000001</v>
       </c>
       <c r="L18" s="72">
         <f t="shared" si="2"/>
@@ -3863,54 +3798,54 @@
       </c>
       <c r="M18" s="72">
         <f t="shared" si="3"/>
-        <v>245999.99999999997</v>
+        <v>262399.99999999994</v>
       </c>
       <c r="N18" s="114">
         <f t="shared" si="4"/>
-        <v>15065931.375999998</v>
+        <v>15822585.575999999</v>
       </c>
       <c r="O18" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$15065931,12</v>
+        <v>$15822586,12</v>
       </c>
       <c r="P18" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$15517909,12</v>
+        <v>$16297263,12</v>
       </c>
       <c r="Q18" s="43" t="str">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B19" s="62">
         <v>17</v>
       </c>
       <c r="C19" s="62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19" s="63"/>
       <c r="F19" s="68">
         <v>6.1</v>
       </c>
       <c r="G19" s="134">
-        <v>10194042.17</v>
+        <v>10897785.17</v>
       </c>
       <c r="H19" s="69"/>
       <c r="I19" s="70"/>
       <c r="J19" s="117">
         <f t="shared" si="0"/>
-        <v>10194042.17</v>
+        <v>10897785.17</v>
       </c>
       <c r="K19" s="71">
         <f t="shared" si="1"/>
-        <v>509702.10850000003</v>
+        <v>544889.2585</v>
       </c>
       <c r="L19" s="72">
         <f t="shared" si="2"/>
@@ -3918,55 +3853,54 @@
       </c>
       <c r="M19" s="72">
         <f t="shared" si="3"/>
-        <v>183000</v>
+        <v>195200</v>
       </c>
       <c r="N19" s="114">
         <f t="shared" si="4"/>
-        <v>10897785.2785</v>
+        <v>11648915.4285</v>
       </c>
       <c r="O19" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$10897785,17</v>
+        <v>$11648915,17</v>
       </c>
       <c r="P19" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$11224719,17</v>
+        <v>$11998383,17</v>
       </c>
       <c r="Q19" s="43" t="str">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" s="62">
         <v>16</v>
       </c>
       <c r="C20" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="62" t="s">
+      <c r="E20" s="63" t="s">
         <v>128</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>129</v>
       </c>
       <c r="F20" s="68">
         <v>5</v>
       </c>
       <c r="G20" s="135">
-        <v>168321.16</v>
-      </c>
-      <c r="H20" s="69">
-        <f>G20</f>
-        <v>168321.16</v>
+        <v>159050.16</v>
+      </c>
+      <c r="H20" s="130">
+        <v>160000</v>
       </c>
       <c r="I20" s="70"/>
       <c r="J20" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-949.83999999999651</v>
       </c>
       <c r="K20" s="71">
         <f t="shared" si="1"/>
@@ -3978,59 +3912,60 @@
       </c>
       <c r="M20" s="72">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="N20" s="114">
         <f t="shared" si="4"/>
-        <v>159050</v>
+        <v>168100.16</v>
       </c>
       <c r="O20" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$159050,16</v>
+        <v>$168100,16</v>
       </c>
       <c r="P20" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$163822,16</v>
+        <v>$173143,16</v>
       </c>
       <c r="Q20" s="43" t="str">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S20" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B21" s="62">
         <v>15</v>
       </c>
       <c r="C21" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="62" t="s">
         <v>131</v>
-      </c>
-      <c r="D21" s="62" t="s">
-        <v>132</v>
       </c>
       <c r="E21" s="62"/>
       <c r="F21" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G21" s="134">
-        <v>264918.15000000002</v>
+        <v>280706.15000000002</v>
       </c>
       <c r="H21" s="69">
-        <v>246000</v>
+        <f>18918+264918.15+946</f>
+        <v>284782.15000000002</v>
       </c>
       <c r="I21" s="70"/>
       <c r="J21" s="117">
         <f t="shared" si="0"/>
-        <v>18918.150000000023</v>
+        <v>-4076</v>
       </c>
       <c r="K21" s="71">
         <f t="shared" si="1"/>
-        <v>945.90750000000116</v>
+        <v>0</v>
       </c>
       <c r="L21" s="72">
         <f t="shared" si="2"/>
@@ -4038,19 +3973,19 @@
       </c>
       <c r="M21" s="72">
         <f t="shared" si="3"/>
-        <v>245999.99999999997</v>
+        <v>262399.99999999994</v>
       </c>
       <c r="N21" s="114">
         <f t="shared" si="4"/>
-        <v>280706.0575</v>
+        <v>273165.99999999994</v>
       </c>
       <c r="O21" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$280706,15</v>
+        <v>$273166,15</v>
       </c>
       <c r="P21" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$289127,15</v>
+        <v>$281361,15</v>
       </c>
       <c r="Q21" s="43" t="str">
         <f t="shared" si="7"/>
@@ -4058,18 +3993,18 @@
       </c>
       <c r="S21" s="42"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B22" s="62">
         <v>20</v>
       </c>
       <c r="C22" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="62" t="s">
         <v>133</v>
-      </c>
-      <c r="D22" s="62" t="s">
-        <v>134</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="68">
@@ -4097,59 +4032,62 @@
       </c>
       <c r="M22" s="72">
         <f t="shared" si="3"/>
-        <v>183000</v>
+        <v>195200</v>
       </c>
       <c r="N22" s="114">
         <f t="shared" si="4"/>
-        <v>194041</v>
+        <v>206241</v>
       </c>
       <c r="O22" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$194041,20</v>
+        <v>$206241,20</v>
       </c>
       <c r="P22" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$199862,20</v>
+        <v>$212428,20</v>
       </c>
       <c r="Q22" s="43" t="str">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="T22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="B23" s="62">
         <v>19</v>
       </c>
       <c r="C23" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="62" t="s">
-        <v>138</v>
-      </c>
       <c r="E23" s="62" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F23" s="68">
         <v>5</v>
       </c>
       <c r="G23" s="134">
-        <v>159050.19</v>
-      </c>
-      <c r="H23" s="69"/>
+        <v>326053.19</v>
+      </c>
+      <c r="H23" s="69">
+        <f>G23</f>
+        <v>326053.19</v>
+      </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71">
         <f t="shared" si="0"/>
-        <v>159050.19</v>
+        <v>0</v>
       </c>
       <c r="K23" s="71">
         <f t="shared" si="1"/>
-        <v>7952.5095000000001</v>
+        <v>0</v>
       </c>
       <c r="L23" s="72">
         <f t="shared" si="2"/>
@@ -4157,53 +4095,52 @@
       </c>
       <c r="M23" s="72">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="N23" s="114">
         <f t="shared" si="4"/>
-        <v>326052.69949999999</v>
+        <v>169050</v>
       </c>
       <c r="O23" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$326053,19</v>
+        <v>$169050,19</v>
       </c>
       <c r="P23" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$335834,19</v>
+        <v>$174122,19</v>
       </c>
       <c r="Q23" s="43" t="str">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24" s="62">
         <v>18</v>
       </c>
       <c r="C24" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="186" t="s">
         <v>139</v>
-      </c>
-      <c r="D24" s="153" t="s">
-        <v>140</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G24" s="134">
-        <v>260842.18</v>
+        <v>253017.18</v>
       </c>
       <c r="H24" s="69">
-        <f>268667.18</f>
-        <v>268667.18</v>
+        <v>262000</v>
       </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71">
         <f t="shared" si="0"/>
-        <v>-7825</v>
+        <v>-8982.820000000007</v>
       </c>
       <c r="K24" s="71">
         <f t="shared" si="1"/>
@@ -4215,29 +4152,29 @@
       </c>
       <c r="M24" s="72">
         <f t="shared" si="3"/>
-        <v>245999.99999999997</v>
+        <v>262399.99999999994</v>
       </c>
       <c r="N24" s="114">
         <f t="shared" si="4"/>
-        <v>253016.99999999997</v>
+        <v>268259.17999999993</v>
       </c>
       <c r="O24" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$253017,18</v>
+        <v>$268259,18</v>
       </c>
       <c r="P24" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$260608,18</v>
+        <v>$276307,18</v>
       </c>
       <c r="Q24" s="43" t="str">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
       <c r="D25" s="75"/>
@@ -4248,11 +4185,11 @@
       </c>
       <c r="G25" s="54">
         <f t="shared" si="8"/>
-        <v>27463169.539999995</v>
+        <v>28979742.899999995</v>
       </c>
       <c r="H25" s="60">
         <f t="shared" si="8"/>
-        <v>2893536.18</v>
+        <v>2907739.07</v>
       </c>
       <c r="I25" s="54">
         <f t="shared" si="8"/>
@@ -4260,11 +4197,11 @@
       </c>
       <c r="J25" s="60">
         <f t="shared" si="8"/>
-        <v>24569633.359999999</v>
+        <v>26072003.829999998</v>
       </c>
       <c r="K25" s="60">
         <f t="shared" si="8"/>
-        <v>1229105.5179999999</v>
+        <v>1304953.4745</v>
       </c>
       <c r="L25" s="60">
         <f t="shared" si="8"/>
@@ -4272,7 +4209,7 @@
       </c>
       <c r="M25" s="60">
         <f t="shared" si="8"/>
-        <v>3000000</v>
+        <v>3200000</v>
       </c>
       <c r="N25" s="115"/>
       <c r="O25" s="77">
@@ -4284,99 +4221,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
-      <c r="R26" s="154" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="168" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28" s="156"/>
-      <c r="F28" s="156"/>
-      <c r="G28" s="156"/>
-      <c r="H28" s="156"/>
-      <c r="I28" s="156"/>
-      <c r="J28" s="156"/>
-      <c r="K28" s="156"/>
-      <c r="L28" s="156"/>
-      <c r="M28" s="156"/>
-      <c r="N28" s="156"/>
-      <c r="O28" s="156"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="156"/>
-      <c r="G29" s="156"/>
-      <c r="H29" s="156"/>
-      <c r="I29" s="156"/>
-      <c r="J29" s="156"/>
-      <c r="K29" s="156"/>
-      <c r="L29" s="156"/>
-      <c r="M29" s="156"/>
-      <c r="N29" s="156"/>
-      <c r="O29" s="156"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="156"/>
-      <c r="I30" s="156"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="156"/>
-      <c r="L30" s="156"/>
-      <c r="M30" s="156"/>
-      <c r="N30" s="156"/>
-      <c r="O30" s="156"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="156"/>
-      <c r="L31" s="156"/>
-      <c r="M31" s="156"/>
-      <c r="N31" s="156"/>
-      <c r="O31" s="156"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="156"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="156"/>
-      <c r="M32" s="156"/>
-      <c r="N32" s="156"/>
-      <c r="O32" s="156"/>
-    </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="156"/>
-      <c r="I33" s="156"/>
-      <c r="J33" s="156"/>
-      <c r="K33" s="156"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="156"/>
-      <c r="N33" s="156"/>
-      <c r="O33" s="156"/>
+      <c r="R26" s="104"/>
+    </row>
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="161" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="154"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="154"/>
+      <c r="O29" s="154"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="154"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="154"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="154"/>
+      <c r="N30" s="154"/>
+      <c r="O30" s="154"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="154"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="154"/>
+      <c r="M32" s="154"/>
+      <c r="N32" s="154"/>
+      <c r="O32" s="154"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="154"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>
@@ -4384,6 +4319,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4396,13 +4338,6 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
